--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Syracuse_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Joe Tea - Peach</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>43.90</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.9</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Joe Tea - Lemon</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>43.90</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>43.9</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Poland Spring - Sport Top</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>66.54</t>
-        </is>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="E4" t="n">
+        <v>66.54000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Almond Milk</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>35.74</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>214.44</t>
-        </is>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="E5" t="n">
+        <v>214.44</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Natalie's - Strawberry Lemonade</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30.45</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Natalie's - Lemonade</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9.30</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>9.30</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Yogurt - Plain (BIB)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>37.80</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>37.80</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Oat Milk</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>16.09</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>96.54</t>
-        </is>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>96.54000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Avocado - Hand Scooped</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>57.63</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>115.26</t>
-        </is>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E10" t="n">
+        <v>115.26</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Pepper Jack (Sliced)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>53.03</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>212.12</t>
-        </is>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="E11" t="n">
+        <v>212.12</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,14 @@
           <t>Cream Cheese</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>62.00</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>186.00</t>
-        </is>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>62</v>
+      </c>
+      <c r="E12" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -751,20 +685,14 @@
           <t>Pastrami (Sliced)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>66.45</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>66.45</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="E13" t="n">
+        <v>66.45</v>
       </c>
     </row>
     <row r="14">
@@ -778,20 +706,14 @@
           <t>Chicken Breast - Retail (cooked)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>59.22</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>296.10</t>
-        </is>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="E14" t="n">
+        <v>296.1</v>
       </c>
     </row>
     <row r="15">
@@ -805,20 +727,14 @@
           <t>PKT Hot Sauce - Cholula</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>16.83</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>16.83</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.83</v>
       </c>
     </row>
     <row r="16">
@@ -832,20 +748,14 @@
           <t>Monin - Vanilla</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>35.21</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>35.21</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="E16" t="n">
+        <v>35.21</v>
       </c>
     </row>
     <row r="17">
@@ -859,20 +769,14 @@
           <t>Swiss (Sliced)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>56.88</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>113.76</t>
-        </is>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="E17" t="n">
+        <v>113.76</v>
       </c>
     </row>
     <row r="18">
@@ -886,20 +790,14 @@
           <t>Bacon (Pre-Cooked)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>38.98</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>467.76</t>
-        </is>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="E18" t="n">
+        <v>467.76</v>
       </c>
     </row>
   </sheetData>
